--- a/data/base_alimentos.xlsx
+++ b/data/base_alimentos.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liummato\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\GitHub\Indicadores-economicos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D7CF2B-62CC-4C2E-B75C-6566663B33F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="base" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="35">
   <si>
     <t>Ene</t>
   </si>
@@ -116,11 +128,26 @@
   <si>
     <t>COPIADO DE INDEC: sh_ipc_aperturas</t>
   </si>
+  <si>
+    <t>carnes</t>
+  </si>
+  <si>
+    <t>pan</t>
+  </si>
+  <si>
+    <t>lacteos</t>
+  </si>
+  <si>
+    <t>fuente</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
   </numFmts>
@@ -201,10 +228,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,7 +511,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -496,17 +523,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9" t="s">
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="J1" s="10" t="s">
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="J1" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4829,7 +4856,7 @@
         <v>1480</v>
       </c>
       <c r="D98" s="1">
-        <v>1300</v>
+        <v>569</v>
       </c>
       <c r="E98" s="1">
         <v>6500</v>
@@ -4839,8 +4866,8 @@
         <v>48</v>
       </c>
       <c r="G98" s="8">
-        <f t="shared" si="6"/>
-        <v>128.47100175746925</v>
+        <f>(D98-D97)/D97*100</f>
+        <v>0</v>
       </c>
       <c r="H98" s="8">
         <f t="shared" si="7"/>
@@ -4887,7 +4914,7 @@
       </c>
       <c r="G99" s="8">
         <f t="shared" si="6"/>
-        <v>-30.76923076923077</v>
+        <v>58.17223198594025</v>
       </c>
       <c r="H99" s="8">
         <f t="shared" si="7"/>
@@ -5433,10 +5460,3256 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>42736</v>
+      </c>
+      <c r="B2">
+        <v>1.5</v>
+      </c>
+      <c r="C2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D2">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>42767</v>
+      </c>
+      <c r="B3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C3">
+        <v>3.1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>42795</v>
+      </c>
+      <c r="B4">
+        <v>2.8</v>
+      </c>
+      <c r="C4">
+        <v>2.6</v>
+      </c>
+      <c r="D4">
+        <v>5.4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>42826</v>
+      </c>
+      <c r="B5">
+        <v>2.1</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+      <c r="D5">
+        <v>2.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>42856</v>
+      </c>
+      <c r="B6">
+        <v>0.9</v>
+      </c>
+      <c r="C6">
+        <v>2.4</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>42887</v>
+      </c>
+      <c r="B7">
+        <v>1.9</v>
+      </c>
+      <c r="C7">
+        <v>3.6</v>
+      </c>
+      <c r="D7">
+        <v>-0.2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>42917</v>
+      </c>
+      <c r="B8">
+        <v>1.8</v>
+      </c>
+      <c r="C8">
+        <v>1.8</v>
+      </c>
+      <c r="D8">
+        <v>0.9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>42948</v>
+      </c>
+      <c r="B9">
+        <v>1.2</v>
+      </c>
+      <c r="C9">
+        <v>0.8</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>42979</v>
+      </c>
+      <c r="B10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C10">
+        <v>0.8</v>
+      </c>
+      <c r="D10">
+        <v>1.6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>43009</v>
+      </c>
+      <c r="B11">
+        <v>0.7</v>
+      </c>
+      <c r="C11">
+        <v>0.2</v>
+      </c>
+      <c r="D11">
+        <v>1.2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>43040</v>
+      </c>
+      <c r="B12">
+        <v>1.2</v>
+      </c>
+      <c r="C12">
+        <v>1.4</v>
+      </c>
+      <c r="D12">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>43070</v>
+      </c>
+      <c r="B13">
+        <v>1.5</v>
+      </c>
+      <c r="C13">
+        <v>0.6</v>
+      </c>
+      <c r="D13">
+        <v>1.3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>43101</v>
+      </c>
+      <c r="B14">
+        <v>1.7</v>
+      </c>
+      <c r="C14">
+        <v>1.2</v>
+      </c>
+      <c r="D14">
+        <v>1.6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>43132</v>
+      </c>
+      <c r="B15">
+        <v>2.8</v>
+      </c>
+      <c r="C15">
+        <v>1.2</v>
+      </c>
+      <c r="D15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>43160</v>
+      </c>
+      <c r="B16">
+        <v>2.8</v>
+      </c>
+      <c r="C16">
+        <v>3.1</v>
+      </c>
+      <c r="D16">
+        <v>3.2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>43191</v>
+      </c>
+      <c r="B17">
+        <v>2.8</v>
+      </c>
+      <c r="C17">
+        <v>3.9</v>
+      </c>
+      <c r="D17">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>43221</v>
+      </c>
+      <c r="B18">
+        <v>5.9</v>
+      </c>
+      <c r="C18">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D18">
+        <v>2.1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>43252</v>
+      </c>
+      <c r="B19">
+        <v>6.9</v>
+      </c>
+      <c r="C19">
+        <v>3.6</v>
+      </c>
+      <c r="D19">
+        <v>5.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>43282</v>
+      </c>
+      <c r="B20">
+        <v>3.6</v>
+      </c>
+      <c r="C20">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D20">
+        <v>2.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>43313</v>
+      </c>
+      <c r="B21">
+        <v>2.7</v>
+      </c>
+      <c r="C21">
+        <v>3.3</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>43344</v>
+      </c>
+      <c r="B22">
+        <v>10.7</v>
+      </c>
+      <c r="C22">
+        <v>7.4</v>
+      </c>
+      <c r="D22">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>43374</v>
+      </c>
+      <c r="B23">
+        <v>5.7</v>
+      </c>
+      <c r="C23">
+        <v>6.4</v>
+      </c>
+      <c r="D23">
+        <v>3.2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>43405</v>
+      </c>
+      <c r="B24">
+        <v>3.4</v>
+      </c>
+      <c r="C24">
+        <v>6.5</v>
+      </c>
+      <c r="D24">
+        <v>1.7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>43435</v>
+      </c>
+      <c r="B25">
+        <v>2.4</v>
+      </c>
+      <c r="C25">
+        <v>3.5</v>
+      </c>
+      <c r="D25">
+        <v>1.2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>43466</v>
+      </c>
+      <c r="B26">
+        <v>2.7</v>
+      </c>
+      <c r="C26">
+        <v>3.3</v>
+      </c>
+      <c r="D26">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>43497</v>
+      </c>
+      <c r="B27">
+        <v>2.7</v>
+      </c>
+      <c r="C27">
+        <v>3.1</v>
+      </c>
+      <c r="D27">
+        <v>10.3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>43525</v>
+      </c>
+      <c r="B28">
+        <v>3.6</v>
+      </c>
+      <c r="C28">
+        <v>7.1</v>
+      </c>
+      <c r="D28">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>43556</v>
+      </c>
+      <c r="B29">
+        <v>3.1</v>
+      </c>
+      <c r="C29">
+        <v>7</v>
+      </c>
+      <c r="D29">
+        <v>1.7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
+        <v>43586</v>
+      </c>
+      <c r="B30">
+        <v>2.9</v>
+      </c>
+      <c r="C30">
+        <v>7.5</v>
+      </c>
+      <c r="D30">
+        <v>-0.4</v>
+      </c>
+      <c r="E30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>43617</v>
+      </c>
+      <c r="B31">
+        <v>2.6</v>
+      </c>
+      <c r="C31">
+        <v>5.8</v>
+      </c>
+      <c r="D31">
+        <v>0.5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
+        <v>43647</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>2.7</v>
+      </c>
+      <c r="D32">
+        <v>0.1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>43678</v>
+      </c>
+      <c r="B33">
+        <v>4.8</v>
+      </c>
+      <c r="C33">
+        <v>2.8</v>
+      </c>
+      <c r="D33">
+        <v>3.7</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>43709</v>
+      </c>
+      <c r="B34">
+        <v>6.8</v>
+      </c>
+      <c r="C34">
+        <v>1.6</v>
+      </c>
+      <c r="D34">
+        <v>6.7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>43739</v>
+      </c>
+      <c r="B35">
+        <v>1.9</v>
+      </c>
+      <c r="C35">
+        <v>3.4</v>
+      </c>
+      <c r="D35">
+        <v>1.6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>43770</v>
+      </c>
+      <c r="B36">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C36">
+        <v>1.5</v>
+      </c>
+      <c r="D36">
+        <v>6.7</v>
+      </c>
+      <c r="E36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>43800</v>
+      </c>
+      <c r="B37">
+        <v>3.4</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>43831</v>
+      </c>
+      <c r="B38">
+        <v>4.2</v>
+      </c>
+      <c r="C38">
+        <v>5.5</v>
+      </c>
+      <c r="D38">
+        <v>5.9</v>
+      </c>
+      <c r="E38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>43862</v>
+      </c>
+      <c r="B39">
+        <v>2.1</v>
+      </c>
+      <c r="C39">
+        <v>1.2</v>
+      </c>
+      <c r="D39">
+        <v>1.8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>43891</v>
+      </c>
+      <c r="B40">
+        <v>2.1</v>
+      </c>
+      <c r="C40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D40">
+        <v>4.3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>43922</v>
+      </c>
+      <c r="B41">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>3.5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
+        <v>43952</v>
+      </c>
+      <c r="B42">
+        <v>0.3</v>
+      </c>
+      <c r="C42">
+        <v>0.8</v>
+      </c>
+      <c r="D42">
+        <v>-0.5</v>
+      </c>
+      <c r="E42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>43983</v>
+      </c>
+      <c r="B43">
+        <v>1.9</v>
+      </c>
+      <c r="C43">
+        <v>0.7</v>
+      </c>
+      <c r="D43">
+        <v>0.9</v>
+      </c>
+      <c r="E43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
+        <v>44013</v>
+      </c>
+      <c r="B44">
+        <v>2.1</v>
+      </c>
+      <c r="C44">
+        <v>1.5</v>
+      </c>
+      <c r="D44">
+        <v>2.5</v>
+      </c>
+      <c r="E44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>44044</v>
+      </c>
+      <c r="B45">
+        <v>1.8</v>
+      </c>
+      <c r="C45">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D45">
+        <v>3.4</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
+        <v>44075</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>-0.6</v>
+      </c>
+      <c r="D46">
+        <v>1.9</v>
+      </c>
+      <c r="E46" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>44105</v>
+      </c>
+      <c r="B47">
+        <v>2.6</v>
+      </c>
+      <c r="C47">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D47">
+        <v>3.5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>44136</v>
+      </c>
+      <c r="B48">
+        <v>2.8</v>
+      </c>
+      <c r="C48">
+        <v>1.8</v>
+      </c>
+      <c r="D48">
+        <v>5.4</v>
+      </c>
+      <c r="E48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>44166</v>
+      </c>
+      <c r="B49">
+        <v>1.2</v>
+      </c>
+      <c r="C49">
+        <v>0.1</v>
+      </c>
+      <c r="D49">
+        <v>13.9</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
+        <v>44197</v>
+      </c>
+      <c r="B50">
+        <v>1.9</v>
+      </c>
+      <c r="C50">
+        <v>2.1</v>
+      </c>
+      <c r="D50">
+        <v>6.4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>44228</v>
+      </c>
+      <c r="B51">
+        <v>3.9</v>
+      </c>
+      <c r="C51">
+        <v>2.1</v>
+      </c>
+      <c r="D51">
+        <v>2.7</v>
+      </c>
+      <c r="E51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>44256</v>
+      </c>
+      <c r="B52">
+        <v>3.7</v>
+      </c>
+      <c r="C52">
+        <v>8.6</v>
+      </c>
+      <c r="D52">
+        <v>6.8</v>
+      </c>
+      <c r="E52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>44287</v>
+      </c>
+      <c r="B53">
+        <v>5.7</v>
+      </c>
+      <c r="C53">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D53">
+        <v>4.7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="4">
+        <v>44317</v>
+      </c>
+      <c r="B54">
+        <v>3.9</v>
+      </c>
+      <c r="C54">
+        <v>2.8</v>
+      </c>
+      <c r="D54">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E54" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
+        <v>44348</v>
+      </c>
+      <c r="B55">
+        <v>4.5</v>
+      </c>
+      <c r="C55">
+        <v>6.2</v>
+      </c>
+      <c r="D55">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="4">
+        <v>44378</v>
+      </c>
+      <c r="B56">
+        <v>3.1</v>
+      </c>
+      <c r="C56">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D56">
+        <v>0.4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
+        <v>44409</v>
+      </c>
+      <c r="B57">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C57">
+        <v>3.2</v>
+      </c>
+      <c r="D57">
+        <v>0.3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
+        <v>44440</v>
+      </c>
+      <c r="B58">
+        <v>3.2</v>
+      </c>
+      <c r="C58">
+        <v>4.7</v>
+      </c>
+      <c r="D58">
+        <v>1.3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>44470</v>
+      </c>
+      <c r="B59">
+        <v>3.2</v>
+      </c>
+      <c r="C59">
+        <v>2.8</v>
+      </c>
+      <c r="D59">
+        <v>1.3</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
+        <v>44501</v>
+      </c>
+      <c r="B60">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C60">
+        <v>-0.6</v>
+      </c>
+      <c r="D60">
+        <v>7.3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
+        <v>44531</v>
+      </c>
+      <c r="B61">
+        <v>2.9</v>
+      </c>
+      <c r="C61">
+        <v>3.3</v>
+      </c>
+      <c r="D61">
+        <v>8.5</v>
+      </c>
+      <c r="E61" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
+        <v>44562</v>
+      </c>
+      <c r="B62">
+        <v>2.9</v>
+      </c>
+      <c r="C62">
+        <v>2.6</v>
+      </c>
+      <c r="D62">
+        <v>1.3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
+        <v>44593</v>
+      </c>
+      <c r="B63">
+        <v>5.8</v>
+      </c>
+      <c r="C63">
+        <v>6.5</v>
+      </c>
+      <c r="D63">
+        <v>5.7</v>
+      </c>
+      <c r="E63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
+        <v>44621</v>
+      </c>
+      <c r="B64">
+        <v>11.6</v>
+      </c>
+      <c r="C64">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D64">
+        <v>7.5</v>
+      </c>
+      <c r="E64" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
+        <v>44652</v>
+      </c>
+      <c r="B65">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C65">
+        <v>7.8</v>
+      </c>
+      <c r="D65">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
+        <v>44682</v>
+      </c>
+      <c r="B66">
+        <v>4.2</v>
+      </c>
+      <c r="C66">
+        <v>4.3</v>
+      </c>
+      <c r="D66">
+        <v>6.5</v>
+      </c>
+      <c r="E66" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
+        <v>44713</v>
+      </c>
+      <c r="B67">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C67">
+        <v>3.8</v>
+      </c>
+      <c r="D67">
+        <v>3.1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
+        <v>44743</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>7.7</v>
+      </c>
+      <c r="D68">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
+        <v>44774</v>
+      </c>
+      <c r="B69">
+        <v>7</v>
+      </c>
+      <c r="C69">
+        <v>9</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
+        <v>44805</v>
+      </c>
+      <c r="B70">
+        <v>5.7</v>
+      </c>
+      <c r="C70">
+        <v>7.4</v>
+      </c>
+      <c r="D70">
+        <v>4.5</v>
+      </c>
+      <c r="E70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
+        <v>44835</v>
+      </c>
+      <c r="B71">
+        <v>6.2</v>
+      </c>
+      <c r="C71">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D71">
+        <v>3.6</v>
+      </c>
+      <c r="E71" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="4">
+        <v>44866</v>
+      </c>
+      <c r="B72">
+        <v>5.9</v>
+      </c>
+      <c r="C72">
+        <v>5.6</v>
+      </c>
+      <c r="D72">
+        <v>0.9</v>
+      </c>
+      <c r="E72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
+        <v>44896</v>
+      </c>
+      <c r="B73">
+        <v>6.7</v>
+      </c>
+      <c r="C73">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="4">
+        <v>44927</v>
+      </c>
+      <c r="B74">
+        <v>3.9</v>
+      </c>
+      <c r="C74">
+        <v>4.7</v>
+      </c>
+      <c r="D74">
+        <v>3.9</v>
+      </c>
+      <c r="E74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
+        <v>44958</v>
+      </c>
+      <c r="B75">
+        <v>6.1</v>
+      </c>
+      <c r="C75">
+        <v>8</v>
+      </c>
+      <c r="D75">
+        <v>21.1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="4">
+        <v>44986</v>
+      </c>
+      <c r="B76">
+        <v>7</v>
+      </c>
+      <c r="C76">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="4">
+        <v>45017</v>
+      </c>
+      <c r="B77">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C77">
+        <v>10.4</v>
+      </c>
+      <c r="D77">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="4">
+        <v>45047</v>
+      </c>
+      <c r="B78">
+        <v>9.5</v>
+      </c>
+      <c r="C78">
+        <v>9.6</v>
+      </c>
+      <c r="D78">
+        <v>1.5</v>
+      </c>
+      <c r="E78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="4">
+        <v>45078</v>
+      </c>
+      <c r="B79">
+        <v>8.9</v>
+      </c>
+      <c r="C79">
+        <v>7</v>
+      </c>
+      <c r="D79">
+        <v>0.9</v>
+      </c>
+      <c r="E79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="4">
+        <v>45108</v>
+      </c>
+      <c r="B80">
+        <v>7.4</v>
+      </c>
+      <c r="C80">
+        <v>7.8</v>
+      </c>
+      <c r="D80">
+        <v>3.1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
+        <v>45139</v>
+      </c>
+      <c r="B81">
+        <v>11.6</v>
+      </c>
+      <c r="C81">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D81">
+        <v>25.6</v>
+      </c>
+      <c r="E81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="4">
+        <v>45170</v>
+      </c>
+      <c r="B82">
+        <v>12.7</v>
+      </c>
+      <c r="C82">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D82">
+        <v>15.9</v>
+      </c>
+      <c r="E82" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="4">
+        <v>45200</v>
+      </c>
+      <c r="B83">
+        <v>11.4</v>
+      </c>
+      <c r="C83">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D83">
+        <v>7.7</v>
+      </c>
+      <c r="E83" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
+        <v>45231</v>
+      </c>
+      <c r="B84">
+        <v>17.7</v>
+      </c>
+      <c r="C84">
+        <v>10</v>
+      </c>
+      <c r="D84">
+        <v>14.6</v>
+      </c>
+      <c r="E84" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="4">
+        <v>45261</v>
+      </c>
+      <c r="B85">
+        <v>30.2</v>
+      </c>
+      <c r="C85">
+        <v>28.4</v>
+      </c>
+      <c r="D85">
+        <v>36.9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="4">
+        <v>45292</v>
+      </c>
+      <c r="B86">
+        <v>23.6</v>
+      </c>
+      <c r="C86">
+        <v>27.7</v>
+      </c>
+      <c r="D86">
+        <v>12.8</v>
+      </c>
+      <c r="E86" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="4">
+        <v>45323</v>
+      </c>
+      <c r="B87">
+        <v>13</v>
+      </c>
+      <c r="C87">
+        <v>16.3</v>
+      </c>
+      <c r="D87">
+        <v>9.1</v>
+      </c>
+      <c r="E87" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="4">
+        <v>45352</v>
+      </c>
+      <c r="B88">
+        <v>8.5</v>
+      </c>
+      <c r="C88">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D88">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="4">
+        <v>45383</v>
+      </c>
+      <c r="B89">
+        <v>5.2</v>
+      </c>
+      <c r="C89">
+        <v>8.4</v>
+      </c>
+      <c r="D89">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E89" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="4">
+        <v>45413</v>
+      </c>
+      <c r="B90">
+        <v>3.8</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>2.5</v>
+      </c>
+      <c r="E90" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="4">
+        <v>45444</v>
+      </c>
+      <c r="B91">
+        <v>3.4</v>
+      </c>
+      <c r="C91">
+        <v>3.2</v>
+      </c>
+      <c r="D91">
+        <v>1.5</v>
+      </c>
+      <c r="E91" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="4">
+        <v>45474</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="C92">
+        <v>2.4</v>
+      </c>
+      <c r="D92">
+        <v>1.7</v>
+      </c>
+      <c r="E92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="4">
+        <v>45505</v>
+      </c>
+      <c r="B93">
+        <v>4.3</v>
+      </c>
+      <c r="C93">
+        <v>4.8</v>
+      </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
+      <c r="E93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="4">
+        <v>45536</v>
+      </c>
+      <c r="B94">
+        <v>2.4</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94">
+        <v>3.1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="4">
+        <v>45566</v>
+      </c>
+      <c r="B95">
+        <v>2.1</v>
+      </c>
+      <c r="C95">
+        <v>2.5</v>
+      </c>
+      <c r="D95">
+        <v>0.9</v>
+      </c>
+      <c r="E95" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="4">
+        <v>45597</v>
+      </c>
+      <c r="B96">
+        <v>1.9</v>
+      </c>
+      <c r="C96">
+        <v>2.5</v>
+      </c>
+      <c r="D96">
+        <v>2.6</v>
+      </c>
+      <c r="E96" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="4">
+        <v>45627</v>
+      </c>
+      <c r="B97">
+        <v>1.7</v>
+      </c>
+      <c r="C97">
+        <v>1.5</v>
+      </c>
+      <c r="D97">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E97" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="4">
+        <v>42736</v>
+      </c>
+      <c r="B98">
+        <v>-7.1428571428571423</v>
+      </c>
+      <c r="C98">
+        <v>-2.6315789473684208</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="4">
+        <v>42767</v>
+      </c>
+      <c r="B99">
+        <v>15.384615384615385</v>
+      </c>
+      <c r="C99">
+        <v>8.1081081081081088</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="4">
+        <v>42795</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>4.5454545454545459</v>
+      </c>
+      <c r="E100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="4">
+        <v>42826</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>5</v>
+      </c>
+      <c r="D101">
+        <v>4.3478260869565215</v>
+      </c>
+      <c r="E101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="4">
+        <v>42856</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>4.7619047619047619</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="4">
+        <v>42887</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="4">
+        <v>42917</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>3.4090909090909087</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
+        <v>42948</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>-3.296703296703297</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="4">
+        <v>42979</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>4.5454545454545459</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="4">
+        <v>43009</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>-4.3478260869565215</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="4">
+        <v>43040</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>9.0909090909090917</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="4">
+        <v>43070</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>-4.1666666666666661</v>
+      </c>
+      <c r="D109">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="E109" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="4">
+        <v>43101</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110">
+        <v>4.3478260869565215</v>
+      </c>
+      <c r="D110">
+        <v>4</v>
+      </c>
+      <c r="E110" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="4">
+        <v>43132</v>
+      </c>
+      <c r="B111">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="C111">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="D111">
+        <v>3.8461538461538463</v>
+      </c>
+      <c r="E111" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="4">
+        <v>43160</v>
+      </c>
+      <c r="B112">
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="E112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="4">
+        <v>43191</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>-3.5714285714285712</v>
+      </c>
+      <c r="E113" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="4">
+        <v>43221</v>
+      </c>
+      <c r="B114">
+        <v>11.111111111111111</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="E114" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="4">
+        <v>43252</v>
+      </c>
+      <c r="B115">
+        <v>12.5</v>
+      </c>
+      <c r="C115">
+        <v>6</v>
+      </c>
+      <c r="D115">
+        <v>7.1428571428571423</v>
+      </c>
+      <c r="E115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="4">
+        <v>43282</v>
+      </c>
+      <c r="E116" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
+        <v>43313</v>
+      </c>
+      <c r="E117" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="4">
+        <v>43344</v>
+      </c>
+      <c r="B118">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="C118">
+        <v>13.20754716981132</v>
+      </c>
+      <c r="D118">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
+        <v>43374</v>
+      </c>
+      <c r="B119">
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="C119">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D119">
+        <v>12.5</v>
+      </c>
+      <c r="E119" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="4">
+        <v>43405</v>
+      </c>
+      <c r="B120">
+        <v>1.6949152542372881</v>
+      </c>
+      <c r="C120">
+        <v>9.375</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
+        <v>43435</v>
+      </c>
+      <c r="B121">
+        <v>-3.3333333333333335</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>4.4444444444444446</v>
+      </c>
+      <c r="E121" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="4">
+        <v>43466</v>
+      </c>
+      <c r="B122">
+        <v>3.4482758620689653</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>1.0638297872340425</v>
+      </c>
+      <c r="E122" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="4">
+        <v>43497</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123">
+        <v>14.285714285714285</v>
+      </c>
+      <c r="D123">
+        <v>15.789473684210526</v>
+      </c>
+      <c r="E123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="4">
+        <v>43525</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>4.5454545454545459</v>
+      </c>
+      <c r="E124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="4">
+        <v>43556</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>12.5</v>
+      </c>
+      <c r="D125">
+        <v>4.3478260869565215</v>
+      </c>
+      <c r="E125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="4">
+        <v>43586</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>-8.3333333333333321</v>
+      </c>
+      <c r="E126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
+        <v>43617</v>
+      </c>
+      <c r="B127">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="C127">
+        <v>4.4444444444444446</v>
+      </c>
+      <c r="D127">
+        <v>1.1363636363636365</v>
+      </c>
+      <c r="E127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="4">
+        <v>43647</v>
+      </c>
+      <c r="B128">
+        <v>-7.1428571428571423</v>
+      </c>
+      <c r="C128">
+        <v>6.3829787234042552</v>
+      </c>
+      <c r="D128">
+        <v>-3.5955056179775284</v>
+      </c>
+      <c r="E128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="4">
+        <v>43678</v>
+      </c>
+      <c r="B129">
+        <v>23.076923076923077</v>
+      </c>
+      <c r="C129">
+        <v>8</v>
+      </c>
+      <c r="D129">
+        <v>11.841491841491845</v>
+      </c>
+      <c r="E129" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="4">
+        <v>43709</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>-7.4074074074074066</v>
+      </c>
+      <c r="D130">
+        <v>4.2100875364735284</v>
+      </c>
+      <c r="E130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="4">
+        <v>43739</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>10</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="4">
+        <v>43770</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>5</v>
+      </c>
+      <c r="E132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="4">
+        <v>43800</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>10.476190476190476</v>
+      </c>
+      <c r="E133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="4">
+        <v>43831</v>
+      </c>
+      <c r="B134">
+        <v>6.25</v>
+      </c>
+      <c r="C134">
+        <v>9.0909090909090917</v>
+      </c>
+      <c r="D134">
+        <v>10.344827586206897</v>
+      </c>
+      <c r="E134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="4">
+        <v>43862</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>-8.3333333333333321</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="4">
+        <v>43891</v>
+      </c>
+      <c r="E136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
+        <v>43922</v>
+      </c>
+      <c r="B137">
+        <v>5.8823529411764701</v>
+      </c>
+      <c r="C137">
+        <v>18.181818181818183</v>
+      </c>
+      <c r="D137">
+        <v>9.375</v>
+      </c>
+      <c r="E137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="4">
+        <v>43952</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="4">
+        <v>43983</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="4">
+        <v>44013</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>7.6923076923076925</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="4">
+        <v>44044</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>-7.1428571428571423</v>
+      </c>
+      <c r="D141">
+        <v>5.7142857142857144</v>
+      </c>
+      <c r="E141" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="4">
+        <v>44075</v>
+      </c>
+      <c r="B142">
+        <v>10</v>
+      </c>
+      <c r="C142">
+        <v>4.6153846153846159</v>
+      </c>
+      <c r="D142">
+        <v>2.7027027027027026</v>
+      </c>
+      <c r="E142" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="4">
+        <v>44105</v>
+      </c>
+      <c r="B143">
+        <v>1.0101010101010102</v>
+      </c>
+      <c r="C143">
+        <v>1.4705882352941175</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="4">
+        <v>44136</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <v>1.4492753623188406</v>
+      </c>
+      <c r="D144">
+        <v>13.157894736842104</v>
+      </c>
+      <c r="E144" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="4">
+        <v>44166</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>16.279069767441861</v>
+      </c>
+      <c r="E145" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="4">
+        <v>44197</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>10</v>
+      </c>
+      <c r="E146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="4">
+        <v>44228</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>5.4545454545454541</v>
+      </c>
+      <c r="E147" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="4">
+        <v>44256</v>
+      </c>
+      <c r="B148">
+        <v>14.285714285714285</v>
+      </c>
+      <c r="C148">
+        <v>8.5714285714285712</v>
+      </c>
+      <c r="D148">
+        <v>3.4482758620689653</v>
+      </c>
+      <c r="E148" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="4">
+        <v>44287</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>5.2631578947368416</v>
+      </c>
+      <c r="D149">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="E149" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="4">
+        <v>44317</v>
+      </c>
+      <c r="B150">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="C150">
+        <v>6.25</v>
+      </c>
+      <c r="D150">
+        <v>4.838709677419355</v>
+      </c>
+      <c r="E150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="4">
+        <v>44348</v>
+      </c>
+      <c r="B151">
+        <v>4</v>
+      </c>
+      <c r="C151">
+        <v>5.8823529411764701</v>
+      </c>
+      <c r="D151">
+        <v>4.6153846153846159</v>
+      </c>
+      <c r="E151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="4">
+        <v>44378</v>
+      </c>
+      <c r="B152">
+        <v>3.8461538461538463</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>-1.4705882352941175</v>
+      </c>
+      <c r="E152" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="4">
+        <v>44409</v>
+      </c>
+      <c r="B153">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>-1.4925373134328357</v>
+      </c>
+      <c r="E153" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="4">
+        <v>44440</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="D154">
+        <v>1.5151515151515151</v>
+      </c>
+      <c r="E154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="4">
+        <v>44470</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>5.2631578947368416</v>
+      </c>
+      <c r="D155">
+        <v>1.4925373134328357</v>
+      </c>
+      <c r="E155" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="4">
+        <v>44501</v>
+      </c>
+      <c r="B156">
+        <v>3.5714285714285712</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>17.573529411764703</v>
+      </c>
+      <c r="E156" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="4">
+        <v>44531</v>
+      </c>
+      <c r="B157">
+        <v>3.4482758620689653</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>8.8180112570356481</v>
+      </c>
+      <c r="E157" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="4">
+        <v>44562</v>
+      </c>
+      <c r="B158">
+        <v>-20</v>
+      </c>
+      <c r="C158">
+        <v>-5</v>
+      </c>
+      <c r="D158">
+        <v>1.7241379310344827</v>
+      </c>
+      <c r="E158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="4">
+        <v>44593</v>
+      </c>
+      <c r="B159">
+        <v>50</v>
+      </c>
+      <c r="C159">
+        <v>26.315789473684209</v>
+      </c>
+      <c r="D159">
+        <v>1.6949152542372881</v>
+      </c>
+      <c r="E159" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="4">
+        <v>44621</v>
+      </c>
+      <c r="B160">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="E160" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="4">
+        <v>44652</v>
+      </c>
+      <c r="B161">
+        <v>9.0909090909090917</v>
+      </c>
+      <c r="C161">
+        <v>12.5</v>
+      </c>
+      <c r="D161">
+        <v>5.2631578947368416</v>
+      </c>
+      <c r="E161" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="4">
+        <v>44682</v>
+      </c>
+      <c r="B162">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="C162">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="D162">
+        <v>5</v>
+      </c>
+      <c r="E162" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="4">
+        <v>44713</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>4.7619047619047619</v>
+      </c>
+      <c r="E163" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="4">
+        <v>44743</v>
+      </c>
+      <c r="B164">
+        <v>16</v>
+      </c>
+      <c r="C164">
+        <v>14.285714285714285</v>
+      </c>
+      <c r="D164">
+        <v>4.5454545454545459</v>
+      </c>
+      <c r="E164" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="4">
+        <v>44774</v>
+      </c>
+      <c r="B165">
+        <v>3.4482758620689653</v>
+      </c>
+      <c r="C165">
+        <v>6.25</v>
+      </c>
+      <c r="D165">
+        <v>-4.3478260869565215</v>
+      </c>
+      <c r="E165" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="4">
+        <v>44805</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+      <c r="C166">
+        <v>5.8823529411764701</v>
+      </c>
+      <c r="D166">
+        <v>8.1818181818181817</v>
+      </c>
+      <c r="E166" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="4">
+        <v>44835</v>
+      </c>
+      <c r="B167">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="C167">
+        <v>11.111111111111111</v>
+      </c>
+      <c r="D167">
+        <v>0.84033613445378152</v>
+      </c>
+      <c r="E167" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="4">
+        <v>44866</v>
+      </c>
+      <c r="B168">
+        <v>9.375</v>
+      </c>
+      <c r="C168">
+        <v>5</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="4">
+        <v>44896</v>
+      </c>
+      <c r="B169">
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+      <c r="D169">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="E169" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="4">
+        <v>44927</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <v>14.285714285714285</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="4">
+        <v>44958</v>
+      </c>
+      <c r="B171">
+        <v>11.111111111111111</v>
+      </c>
+      <c r="C171">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="D171">
+        <v>23.076923076923077</v>
+      </c>
+      <c r="E171" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="4">
+        <v>44986</v>
+      </c>
+      <c r="B172">
+        <v>5</v>
+      </c>
+      <c r="C172">
+        <v>8</v>
+      </c>
+      <c r="D172">
+        <v>6.25</v>
+      </c>
+      <c r="E172" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="4">
+        <v>45017</v>
+      </c>
+      <c r="B173">
+        <v>9.5238095238095237</v>
+      </c>
+      <c r="C173">
+        <v>11.111111111111111</v>
+      </c>
+      <c r="D173">
+        <v>10.588235294117647</v>
+      </c>
+      <c r="E173" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="4">
+        <v>45047</v>
+      </c>
+      <c r="B174">
+        <v>17.391304347826086</v>
+      </c>
+      <c r="C174">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="D174">
+        <v>-1.5957446808510638</v>
+      </c>
+      <c r="E174" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="4">
+        <v>45078</v>
+      </c>
+      <c r="B175">
+        <v>7.4074074074074066</v>
+      </c>
+      <c r="C175">
+        <v>12.903225806451612</v>
+      </c>
+      <c r="D175">
+        <v>2.7027027027027026</v>
+      </c>
+      <c r="E175" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="4">
+        <v>45108</v>
+      </c>
+      <c r="B176">
+        <v>3.4482758620689653</v>
+      </c>
+      <c r="C176">
+        <v>11.428571428571429</v>
+      </c>
+      <c r="D176">
+        <v>4.7368421052631584</v>
+      </c>
+      <c r="E176" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="4">
+        <v>45139</v>
+      </c>
+      <c r="B177">
+        <v>25</v>
+      </c>
+      <c r="C177">
+        <v>15.384615384615385</v>
+      </c>
+      <c r="D177">
+        <v>49.748743718592962</v>
+      </c>
+      <c r="E177" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="4">
+        <v>45170</v>
+      </c>
+      <c r="B178">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="C178">
+        <v>8.8888888888888893</v>
+      </c>
+      <c r="D178">
+        <v>-2.6845637583892619</v>
+      </c>
+      <c r="E178" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="4">
+        <v>45200</v>
+      </c>
+      <c r="B179">
+        <v>11.25</v>
+      </c>
+      <c r="C179">
+        <v>2.0408163265306123</v>
+      </c>
+      <c r="D179">
+        <v>13.793103448275861</v>
+      </c>
+      <c r="E179" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="4">
+        <v>45231</v>
+      </c>
+      <c r="B180">
+        <v>12.359550561797752</v>
+      </c>
+      <c r="C180">
+        <v>13.8</v>
+      </c>
+      <c r="D180">
+        <v>21.212121212121211</v>
+      </c>
+      <c r="E180" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="4">
+        <v>45261</v>
+      </c>
+      <c r="B181">
+        <v>48</v>
+      </c>
+      <c r="D181">
+        <v>62.5</v>
+      </c>
+      <c r="E181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="4">
+        <v>45292</v>
+      </c>
+      <c r="B182">
+        <v>4.7297297297297298</v>
+      </c>
+      <c r="C182">
+        <v>-30.76923076923077</v>
+      </c>
+      <c r="D182">
+        <v>-10.76923076923077</v>
+      </c>
+      <c r="E182" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="4">
+        <v>45323</v>
+      </c>
+      <c r="B183">
+        <v>16.129032258064516</v>
+      </c>
+      <c r="C183">
+        <v>11.111111111111111</v>
+      </c>
+      <c r="D183">
+        <v>12.068965517241379</v>
+      </c>
+      <c r="E183" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="4">
+        <v>45352</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>20</v>
+      </c>
+      <c r="D184">
+        <v>-3.0769230769230771</v>
+      </c>
+      <c r="E184" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="4">
+        <v>45383</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>6.3492063492063489</v>
+      </c>
+      <c r="E185" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="4">
+        <v>45413</v>
+      </c>
+      <c r="C186">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="D186">
+        <v>-2.9850746268656714</v>
+      </c>
+      <c r="E186" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="4">
+        <v>45444</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="4">
+        <v>45474</v>
+      </c>
+      <c r="B188">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="C188">
+        <v>7.6923076923076925</v>
+      </c>
+      <c r="D188">
+        <v>6.1538461538461542</v>
+      </c>
+      <c r="E188" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="4">
+        <v>45505</v>
+      </c>
+      <c r="B189">
+        <v>4.7619047619047619</v>
+      </c>
+      <c r="C189">
+        <v>7.1428571428571423</v>
+      </c>
+      <c r="D189">
+        <v>1.4492753623188406</v>
+      </c>
+      <c r="E189" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="4">
+        <v>45536</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <v>-6.666666666666667</v>
+      </c>
+      <c r="D190">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="E190" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="4">
+        <v>45566</v>
+      </c>
+      <c r="B191">
+        <v>13.636363636363635</v>
+      </c>
+      <c r="C191">
+        <v>7.1428571428571423</v>
+      </c>
+      <c r="D191">
+        <v>0.28653295128939826</v>
+      </c>
+      <c r="E191" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192" s="4">
+        <v>45597</v>
+      </c>
+      <c r="B192">
+        <v>-8</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193" s="4">
+        <v>45627</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>35.714285714285715</v>
+      </c>
+      <c r="E193" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>